--- a/seminar_03/problem_4.14_solution.xlsx
+++ b/seminar_03/problem_4.14_solution.xlsx
@@ -564,6 +564,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
@@ -895,6 +896,7 @@
         <v/>
       </c>
     </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
@@ -945,6 +947,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -955,9 +958,10 @@
         <f>COUNT(Данные!$B$6:$B$21)</f>
         <v/>
       </c>
-      <c r="C4" s="10">
-        <f>СЧЁТ(столбец y)</f>
-        <v/>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>=СЧЁТ(столбец y)</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -970,9 +974,10 @@
         <f>AVERAGE(Данные!$C$6:$C$21)</f>
         <v/>
       </c>
-      <c r="C5" s="10">
-        <f>СРЗНАЧ(столбец x)</f>
-        <v/>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>=СРЗНАЧ(столбец x)</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -985,9 +990,10 @@
         <f>AVERAGE(Данные!$B$6:$B$21)</f>
         <v/>
       </c>
-      <c r="C6" s="10">
-        <f>СРЗНАЧ(столбец y)</f>
-        <v/>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>=СРЗНАЧ(столбец y)</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -1000,9 +1006,10 @@
         <f>DEVSQ(Данные!$C$6:$C$21)</f>
         <v/>
       </c>
-      <c r="C7" s="10">
-        <f>КВАДРОТКЛ(столбец x)</f>
-        <v/>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>=КВАДРОТКЛ(столбец x)</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -1015,9 +1022,10 @@
         <f>SUMPRODUCT(Данные!$C$6:$C$21-B5,Данные!$B$6:$B$21-B6)</f>
         <v/>
       </c>
-      <c r="C8" s="10">
-        <f>СУММПРОИЗВ(x − x̄; y − ȳ)</f>
-        <v/>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>=СУММПРОИЗВ(x − x̄; y − ȳ)</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -1053,6 +1061,7 @@
         <v/>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
@@ -1519,6 +1528,7 @@
         <v/>
       </c>
     </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
         <is>
@@ -1584,9 +1594,10 @@
         <f>TDIST(ABS(B36),B4-2,2)</f>
         <v/>
       </c>
-      <c r="C37" s="10">
-        <f>СТЬЮДРАСП(|t|; n − 2; 2)</f>
-        <v/>
+      <c r="C37" s="10" t="inlineStr">
+        <is>
+          <t>=СТЬЮДРАСП(|t|; n − 2; 2)</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1623,6 +1634,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="22" t="inlineStr">
         <is>
@@ -1795,6 +1807,7 @@
         <v/>
       </c>
     </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
@@ -1844,6 +1857,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
@@ -1963,6 +1977,7 @@
         <v/>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
@@ -2001,6 +2016,7 @@
         </is>
       </c>
     </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
@@ -2033,6 +2049,7 @@
         </is>
       </c>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
@@ -2073,6 +2090,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -2169,9 +2187,10 @@
         <f>FINV(0.05,B9,B8-2*B9)</f>
         <v/>
       </c>
-      <c r="C11" s="10">
-        <f>FРАСПОБР(0,05; k; n − 2k)</f>
-        <v/>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>=FРАСПОБР(0,05; k; n − 2k)</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -2184,9 +2203,10 @@
         <f>FDIST(B10,B9,B8-2*B9)</f>
         <v/>
       </c>
-      <c r="C12" s="10">
-        <f>FРАСП(F; k; n − 2k)</f>
-        <v/>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>=FРАСП(F; k; n − 2k)</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -2200,6 +2220,7 @@
         <v/>
       </c>
     </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
@@ -2251,6 +2272,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
@@ -2640,6 +2662,7 @@
         <v/>
       </c>
     </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
@@ -2735,6 +2758,8 @@
         </is>
       </c>
     </row>
+    <row r="28"/>
+    <row r="29"/>
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
         <is>
@@ -2775,6 +2800,7 @@
         <v/>
       </c>
     </row>
+    <row r="34"/>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
